--- a/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
+++ b/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Ibrahim\Statistical-Analysis\Project-7 ---\V2\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-7 ---\V3\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD247EBD-B15C-4ECC-960E-B881B321C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36219FE-9C3F-4D9F-A6DA-59FC341E0D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11309" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11309" uniqueCount="265">
   <si>
     <t>mobile</t>
   </si>
@@ -811,7 +811,10 @@
     <t>negative</t>
   </si>
   <si>
-    <t>BCS</t>
+    <t>Biopsy</t>
+  </si>
+  <si>
+    <t>No Surgery</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1592,7 @@
         <v>105</v>
       </c>
       <c r="AT2" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU2" t="s">
         <v>118</v>
@@ -1882,7 +1885,7 @@
         <v>111</v>
       </c>
       <c r="AT3" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU3" t="s">
         <v>118</v>
@@ -2166,7 +2169,7 @@
         <v>107</v>
       </c>
       <c r="AT4" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU4" t="s">
         <v>118</v>
@@ -2453,7 +2456,7 @@
         <v>107</v>
       </c>
       <c r="AT5" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU5" t="s">
         <v>118</v>
@@ -2749,7 +2752,7 @@
         <v>107</v>
       </c>
       <c r="AT6" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU6" t="s">
         <v>118</v>
@@ -3030,7 +3033,7 @@
         <v>107</v>
       </c>
       <c r="AT7" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU7" t="s">
         <v>118</v>
@@ -3308,7 +3311,7 @@
         <v>105</v>
       </c>
       <c r="AT8" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU8" t="s">
         <v>118</v>
@@ -3595,7 +3598,7 @@
         <v>107</v>
       </c>
       <c r="AT9" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU9" t="s">
         <v>118</v>
@@ -3888,7 +3891,7 @@
         <v>107</v>
       </c>
       <c r="AT10" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU10" t="s">
         <v>118</v>
@@ -4169,7 +4172,7 @@
         <v>107</v>
       </c>
       <c r="AT11" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU11" t="s">
         <v>118</v>
@@ -4450,7 +4453,7 @@
         <v>107</v>
       </c>
       <c r="AT12" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU12" t="s">
         <v>118</v>
@@ -4740,7 +4743,7 @@
         <v>107</v>
       </c>
       <c r="AT13" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU13" t="s">
         <v>118</v>
@@ -5027,7 +5030,7 @@
         <v>107</v>
       </c>
       <c r="AT14" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU14" t="s">
         <v>118</v>
@@ -5305,7 +5308,7 @@
         <v>107</v>
       </c>
       <c r="AT15" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU15" t="s">
         <v>118</v>
@@ -5592,7 +5595,7 @@
         <v>111</v>
       </c>
       <c r="AT16" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU16" t="s">
         <v>118</v>
@@ -5882,7 +5885,7 @@
         <v>107</v>
       </c>
       <c r="AT17" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU17" t="s">
         <v>118</v>
@@ -6175,7 +6178,7 @@
         <v>107</v>
       </c>
       <c r="AT18" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU18" t="s">
         <v>118</v>
@@ -6462,7 +6465,7 @@
         <v>107</v>
       </c>
       <c r="AT19" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU19" t="s">
         <v>118</v>
@@ -6755,7 +6758,7 @@
         <v>111</v>
       </c>
       <c r="AT20" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU20" t="s">
         <v>118</v>
@@ -7042,7 +7045,7 @@
         <v>107</v>
       </c>
       <c r="AT21" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU21" t="s">
         <v>118</v>
@@ -7332,7 +7335,7 @@
         <v>107</v>
       </c>
       <c r="AT22" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU22" t="s">
         <v>118</v>
@@ -7619,7 +7622,7 @@
         <v>111</v>
       </c>
       <c r="AT23" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU23" t="s">
         <v>118</v>
@@ -7912,7 +7915,7 @@
         <v>107</v>
       </c>
       <c r="AT24" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU24" t="s">
         <v>118</v>
@@ -8205,7 +8208,7 @@
         <v>111</v>
       </c>
       <c r="AT25" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU25" t="s">
         <v>118</v>
@@ -8492,7 +8495,7 @@
         <v>107</v>
       </c>
       <c r="AT26" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU26" t="s">
         <v>118</v>
@@ -8779,7 +8782,7 @@
         <v>111</v>
       </c>
       <c r="AT27" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU27" t="s">
         <v>118</v>
@@ -9069,7 +9072,7 @@
         <v>107</v>
       </c>
       <c r="AT28" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU28" t="s">
         <v>118</v>
@@ -9362,7 +9365,7 @@
         <v>111</v>
       </c>
       <c r="AT29" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU29" t="s">
         <v>118</v>
@@ -9652,7 +9655,7 @@
         <v>111</v>
       </c>
       <c r="AT30" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU30" t="s">
         <v>118</v>
@@ -9942,7 +9945,7 @@
         <v>111</v>
       </c>
       <c r="AT31" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU31" t="s">
         <v>118</v>
@@ -10235,7 +10238,7 @@
         <v>111</v>
       </c>
       <c r="AT32" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU32" t="s">
         <v>118</v>
@@ -10519,7 +10522,7 @@
         <v>107</v>
       </c>
       <c r="AT33" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU33" t="s">
         <v>118</v>
@@ -10809,7 +10812,7 @@
         <v>111</v>
       </c>
       <c r="AT34" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU34" t="s">
         <v>118</v>
@@ -11102,7 +11105,7 @@
         <v>111</v>
       </c>
       <c r="AT35" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU35" t="s">
         <v>118</v>
@@ -11395,7 +11398,7 @@
         <v>111</v>
       </c>
       <c r="AT36" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU36" t="s">
         <v>118</v>
@@ -11679,7 +11682,7 @@
         <v>111</v>
       </c>
       <c r="AT37" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU37" t="s">
         <v>118</v>
@@ -11960,7 +11963,7 @@
         <v>107</v>
       </c>
       <c r="AT38" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU38" t="s">
         <v>118</v>
@@ -12244,7 +12247,7 @@
         <v>111</v>
       </c>
       <c r="AT39" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU39" t="s">
         <v>118</v>
@@ -12534,7 +12537,7 @@
         <v>111</v>
       </c>
       <c r="AT40" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU40" t="s">
         <v>118</v>
@@ -12818,7 +12821,7 @@
         <v>107</v>
       </c>
       <c r="AT41" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU41" t="s">
         <v>118</v>
@@ -13111,7 +13114,7 @@
         <v>111</v>
       </c>
       <c r="AT42" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU42" t="s">
         <v>118</v>
@@ -13401,7 +13404,7 @@
         <v>107</v>
       </c>
       <c r="AT43" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU43" t="s">
         <v>118</v>
@@ -13682,7 +13685,7 @@
         <v>111</v>
       </c>
       <c r="AT44" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU44" t="s">
         <v>118</v>
@@ -13975,7 +13978,7 @@
         <v>111</v>
       </c>
       <c r="AT45" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU45" t="s">
         <v>118</v>
@@ -14259,7 +14262,7 @@
         <v>107</v>
       </c>
       <c r="AT46" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU46" t="s">
         <v>118</v>
@@ -14546,7 +14549,7 @@
         <v>111</v>
       </c>
       <c r="AT47" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU47" t="s">
         <v>118</v>
@@ -14833,7 +14836,7 @@
         <v>111</v>
       </c>
       <c r="AT48" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU48" t="s">
         <v>118</v>
@@ -15129,7 +15132,7 @@
         <v>107</v>
       </c>
       <c r="AT49" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU49" t="s">
         <v>118</v>
@@ -15413,7 +15416,7 @@
         <v>111</v>
       </c>
       <c r="AT50" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU50" t="s">
         <v>118</v>
@@ -15712,7 +15715,7 @@
         <v>111</v>
       </c>
       <c r="AT51" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU51" t="s">
         <v>118</v>
@@ -16002,7 +16005,7 @@
         <v>111</v>
       </c>
       <c r="AT52" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU52" t="s">
         <v>105</v>
@@ -16295,7 +16298,7 @@
         <v>111</v>
       </c>
       <c r="AT53" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU53" t="s">
         <v>118</v>
@@ -16582,7 +16585,7 @@
         <v>107</v>
       </c>
       <c r="AT54" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU54" t="s">
         <v>118</v>
@@ -16869,7 +16872,7 @@
         <v>107</v>
       </c>
       <c r="AT55" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU55" t="s">
         <v>118</v>
@@ -17159,7 +17162,7 @@
         <v>111</v>
       </c>
       <c r="AT56" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU56" t="s">
         <v>118</v>
@@ -17452,7 +17455,7 @@
         <v>111</v>
       </c>
       <c r="AT57" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU57" t="s">
         <v>118</v>
@@ -17733,7 +17736,7 @@
         <v>111</v>
       </c>
       <c r="AT58" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU58" t="s">
         <v>118</v>
@@ -18029,7 +18032,7 @@
         <v>107</v>
       </c>
       <c r="AT59" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU59" t="s">
         <v>118</v>
@@ -18319,7 +18322,7 @@
         <v>111</v>
       </c>
       <c r="AT60" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU60" t="s">
         <v>118</v>
@@ -18618,7 +18621,7 @@
         <v>111</v>
       </c>
       <c r="AT61" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU61" t="s">
         <v>118</v>
@@ -18905,7 +18908,7 @@
         <v>107</v>
       </c>
       <c r="AT62" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU62" t="s">
         <v>118</v>
@@ -19201,7 +19204,7 @@
         <v>107</v>
       </c>
       <c r="AT63" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU63" t="s">
         <v>118</v>
@@ -19488,7 +19491,7 @@
         <v>111</v>
       </c>
       <c r="AT64" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU64" t="s">
         <v>118</v>
@@ -19775,7 +19778,7 @@
         <v>111</v>
       </c>
       <c r="AT65" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU65" t="s">
         <v>118</v>
@@ -20065,7 +20068,7 @@
         <v>111</v>
       </c>
       <c r="AT66" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU66" t="s">
         <v>118</v>
@@ -20349,7 +20352,7 @@
         <v>107</v>
       </c>
       <c r="AT67" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU67" t="s">
         <v>118</v>
@@ -20633,7 +20636,7 @@
         <v>107</v>
       </c>
       <c r="AT68" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU68" t="s">
         <v>118</v>
@@ -20923,7 +20926,7 @@
         <v>111</v>
       </c>
       <c r="AT69" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU69" t="s">
         <v>118</v>
@@ -21213,7 +21216,7 @@
         <v>111</v>
       </c>
       <c r="AT70" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU70" t="s">
         <v>118</v>
@@ -21512,7 +21515,7 @@
         <v>107</v>
       </c>
       <c r="AT71" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU71" t="s">
         <v>118</v>
@@ -21802,7 +21805,7 @@
         <v>111</v>
       </c>
       <c r="AT72" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU72" t="s">
         <v>118</v>
@@ -22092,7 +22095,7 @@
         <v>107</v>
       </c>
       <c r="AT73" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU73" t="s">
         <v>118</v>
@@ -22379,7 +22382,7 @@
         <v>107</v>
       </c>
       <c r="AT74" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU74" t="s">
         <v>118</v>
@@ -22678,7 +22681,7 @@
         <v>107</v>
       </c>
       <c r="AT75" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU75" t="s">
         <v>118</v>
@@ -22962,7 +22965,7 @@
         <v>111</v>
       </c>
       <c r="AT76" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU76" t="s">
         <v>118</v>
@@ -23252,7 +23255,7 @@
         <v>107</v>
       </c>
       <c r="AT77" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU77" t="s">
         <v>118</v>
@@ -23536,7 +23539,7 @@
         <v>111</v>
       </c>
       <c r="AT78" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU78" t="s">
         <v>118</v>
@@ -23832,7 +23835,7 @@
         <v>107</v>
       </c>
       <c r="AT79" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU79" t="s">
         <v>118</v>
@@ -24122,7 +24125,7 @@
         <v>107</v>
       </c>
       <c r="AT80" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU80" t="s">
         <v>118</v>
@@ -24406,7 +24409,7 @@
         <v>107</v>
       </c>
       <c r="AT81" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU81" t="s">
         <v>118</v>
@@ -24693,7 +24696,7 @@
         <v>111</v>
       </c>
       <c r="AT82" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU82" t="s">
         <v>118</v>
@@ -24986,7 +24989,7 @@
         <v>107</v>
       </c>
       <c r="AT83" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU83" t="s">
         <v>118</v>
@@ -25276,7 +25279,7 @@
         <v>111</v>
       </c>
       <c r="AT84" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU84" t="s">
         <v>118</v>
@@ -25566,7 +25569,7 @@
         <v>107</v>
       </c>
       <c r="AT85" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU85" t="s">
         <v>118</v>
@@ -25856,7 +25859,7 @@
         <v>107</v>
       </c>
       <c r="AT86" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU86" t="s">
         <v>118</v>
@@ -26146,7 +26149,7 @@
         <v>111</v>
       </c>
       <c r="AT87" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU87" t="s">
         <v>118</v>
@@ -26433,7 +26436,7 @@
         <v>107</v>
       </c>
       <c r="AT88" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU88" t="s">
         <v>118</v>
@@ -26723,7 +26726,7 @@
         <v>111</v>
       </c>
       <c r="AT89" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU89" t="s">
         <v>118</v>
@@ -27013,7 +27016,7 @@
         <v>107</v>
       </c>
       <c r="AT90" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU90" t="s">
         <v>118</v>
@@ -27306,7 +27309,7 @@
         <v>111</v>
       </c>
       <c r="AT91" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU91" t="s">
         <v>118</v>
@@ -27883,7 +27886,7 @@
         <v>111</v>
       </c>
       <c r="AT93" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU93" t="s">
         <v>118</v>
@@ -28176,7 +28179,7 @@
         <v>111</v>
       </c>
       <c r="AT94" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU94" t="s">
         <v>118</v>
@@ -28475,7 +28478,7 @@
         <v>111</v>
       </c>
       <c r="AT95" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU95" t="s">
         <v>118</v>
@@ -28765,7 +28768,7 @@
         <v>107</v>
       </c>
       <c r="AT96" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU96" t="s">
         <v>118</v>
@@ -29055,7 +29058,7 @@
         <v>111</v>
       </c>
       <c r="AT97" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU97" t="s">
         <v>118</v>
@@ -29348,7 +29351,7 @@
         <v>111</v>
       </c>
       <c r="AT98" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU98" t="s">
         <v>118</v>
@@ -29638,7 +29641,7 @@
         <v>111</v>
       </c>
       <c r="AT99" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU99" t="s">
         <v>118</v>
@@ -29937,7 +29940,7 @@
         <v>111</v>
       </c>
       <c r="AT100" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU100" t="s">
         <v>118</v>
@@ -30215,7 +30218,7 @@
         <v>111</v>
       </c>
       <c r="AT101" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU101" t="s">
         <v>118</v>
@@ -30502,7 +30505,7 @@
         <v>111</v>
       </c>
       <c r="AT102" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU102" t="s">
         <v>118</v>
@@ -30792,7 +30795,7 @@
         <v>111</v>
       </c>
       <c r="AT103" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU103" t="s">
         <v>118</v>
@@ -31369,7 +31372,7 @@
         <v>111</v>
       </c>
       <c r="AT105" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU105" t="s">
         <v>118</v>
@@ -31943,7 +31946,7 @@
         <v>111</v>
       </c>
       <c r="AT107" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU107" t="s">
         <v>111</v>
@@ -32230,7 +32233,7 @@
         <v>111</v>
       </c>
       <c r="AT108" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU108" t="s">
         <v>118</v>
@@ -32517,7 +32520,7 @@
         <v>111</v>
       </c>
       <c r="AT109" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU109" t="s">
         <v>118</v>
@@ -32804,7 +32807,7 @@
         <v>107</v>
       </c>
       <c r="AT110" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU110" t="s">
         <v>118</v>
@@ -33091,7 +33094,7 @@
         <v>111</v>
       </c>
       <c r="AT111" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU111" t="s">
         <v>118</v>
@@ -33378,7 +33381,7 @@
         <v>111</v>
       </c>
       <c r="AT112" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU112" t="s">
         <v>118</v>
@@ -33668,7 +33671,7 @@
         <v>107</v>
       </c>
       <c r="AT113" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU113" t="s">
         <v>118</v>
@@ -33961,7 +33964,7 @@
         <v>111</v>
       </c>
       <c r="AT114" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU114" t="s">
         <v>118</v>
@@ -34248,7 +34251,7 @@
         <v>111</v>
       </c>
       <c r="AT115" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU115" t="s">
         <v>118</v>
@@ -34541,7 +34544,7 @@
         <v>111</v>
       </c>
       <c r="AT116" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU116" t="s">
         <v>118</v>
@@ -34822,7 +34825,7 @@
         <v>111</v>
       </c>
       <c r="AT117" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU117" t="s">
         <v>118</v>
@@ -35106,7 +35109,7 @@
         <v>111</v>
       </c>
       <c r="AT118" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU118" t="s">
         <v>118</v>
@@ -35393,7 +35396,7 @@
         <v>111</v>
       </c>
       <c r="AT119" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU119" t="s">
         <v>118</v>
@@ -35683,7 +35686,7 @@
         <v>111</v>
       </c>
       <c r="AT120" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU120" t="s">
         <v>118</v>
@@ -35967,7 +35970,7 @@
         <v>111</v>
       </c>
       <c r="AT121" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU121" t="s">
         <v>118</v>
@@ -36544,7 +36547,7 @@
         <v>111</v>
       </c>
       <c r="AT123" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU123" t="s">
         <v>118</v>
@@ -36831,7 +36834,7 @@
         <v>111</v>
       </c>
       <c r="AT124" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU124" t="s">
         <v>118</v>
@@ -37695,7 +37698,7 @@
         <v>111</v>
       </c>
       <c r="AT127" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU127" t="s">
         <v>118</v>
@@ -37982,7 +37985,7 @@
         <v>111</v>
       </c>
       <c r="AT128" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU128" t="s">
         <v>118</v>
@@ -38568,7 +38571,7 @@
         <v>107</v>
       </c>
       <c r="AT130" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU130" t="s">
         <v>118</v>
@@ -38855,7 +38858,7 @@
         <v>111</v>
       </c>
       <c r="AT131" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="AU131" t="s">
         <v>118</v>
@@ -39429,7 +39432,7 @@
         <v>107</v>
       </c>
       <c r="AT133" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU133" t="s">
         <v>118</v>
@@ -39716,7 +39719,7 @@
         <v>111</v>
       </c>
       <c r="AT134" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU134" t="s">
         <v>118</v>
@@ -40006,7 +40009,7 @@
         <v>107</v>
       </c>
       <c r="AT135" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="AU135" t="s">
         <v>118</v>
@@ -40293,7 +40296,7 @@
         <v>107</v>
       </c>
       <c r="AT136" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="AU136" t="s">
         <v>118</v>

--- a/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
+++ b/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-7 ---\V3\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36219FE-9C3F-4D9F-A6DA-59FC341E0D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABA3EAE-3466-4B47-AD2C-0366604A3AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9765" yWindow="60" windowWidth="17250" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11309" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11309" uniqueCount="264">
   <si>
     <t>mobile</t>
   </si>
@@ -802,9 +802,6 @@
     <t xml:space="preserve">&gt;3 site </t>
   </si>
   <si>
-    <t>&gt;3site</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 site </t>
   </si>
   <si>
@@ -1157,6 +1154,7 @@
   <dimension ref="A1:DA136"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="43" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1885,7 +1883,7 @@
         <v>111</v>
       </c>
       <c r="AT3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU3" t="s">
         <v>118</v>
@@ -2450,7 +2448,7 @@
         <v>157</v>
       </c>
       <c r="AR5" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="AS5" t="s">
         <v>107</v>
@@ -2462,7 +2460,7 @@
         <v>118</v>
       </c>
       <c r="AV5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AW5" t="s">
         <v>120</v>
@@ -2752,7 +2750,7 @@
         <v>107</v>
       </c>
       <c r="AT6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU6" t="s">
         <v>118</v>
@@ -3033,7 +3031,7 @@
         <v>107</v>
       </c>
       <c r="AT7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU7" t="s">
         <v>118</v>
@@ -3305,13 +3303,13 @@
         <v>169</v>
       </c>
       <c r="AR8" t="s">
-        <v>259</v>
+        <v>147</v>
       </c>
       <c r="AS8" t="s">
         <v>105</v>
       </c>
       <c r="AT8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU8" t="s">
         <v>118</v>
@@ -3891,7 +3889,7 @@
         <v>107</v>
       </c>
       <c r="AT10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU10" t="s">
         <v>118</v>
@@ -4172,7 +4170,7 @@
         <v>107</v>
       </c>
       <c r="AT11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU11" t="s">
         <v>118</v>
@@ -5030,7 +5028,7 @@
         <v>107</v>
       </c>
       <c r="AT14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU14" t="s">
         <v>118</v>
@@ -5308,7 +5306,7 @@
         <v>107</v>
       </c>
       <c r="AT15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU15" t="s">
         <v>118</v>
@@ -5595,7 +5593,7 @@
         <v>111</v>
       </c>
       <c r="AT16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU16" t="s">
         <v>118</v>
@@ -5885,7 +5883,7 @@
         <v>107</v>
       </c>
       <c r="AT17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU17" t="s">
         <v>118</v>
@@ -6178,7 +6176,7 @@
         <v>107</v>
       </c>
       <c r="AT18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU18" t="s">
         <v>118</v>
@@ -6465,7 +6463,7 @@
         <v>107</v>
       </c>
       <c r="AT19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU19" t="s">
         <v>118</v>
@@ -7335,7 +7333,7 @@
         <v>107</v>
       </c>
       <c r="AT22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU22" t="s">
         <v>118</v>
@@ -7622,7 +7620,7 @@
         <v>111</v>
       </c>
       <c r="AT23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU23" t="s">
         <v>118</v>
@@ -8208,7 +8206,7 @@
         <v>111</v>
       </c>
       <c r="AT25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU25" t="s">
         <v>118</v>
@@ -8495,7 +8493,7 @@
         <v>107</v>
       </c>
       <c r="AT26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU26" t="s">
         <v>118</v>
@@ -8782,7 +8780,7 @@
         <v>111</v>
       </c>
       <c r="AT27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU27" t="s">
         <v>118</v>
@@ -9072,7 +9070,7 @@
         <v>107</v>
       </c>
       <c r="AT28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU28" t="s">
         <v>118</v>
@@ -9655,7 +9653,7 @@
         <v>111</v>
       </c>
       <c r="AT30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU30" t="s">
         <v>118</v>
@@ -10238,7 +10236,7 @@
         <v>111</v>
       </c>
       <c r="AT32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU32" t="s">
         <v>118</v>
@@ -10522,7 +10520,7 @@
         <v>107</v>
       </c>
       <c r="AT33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU33" t="s">
         <v>118</v>
@@ -10812,7 +10810,7 @@
         <v>111</v>
       </c>
       <c r="AT34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU34" t="s">
         <v>118</v>
@@ -11398,7 +11396,7 @@
         <v>111</v>
       </c>
       <c r="AT36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU36" t="s">
         <v>118</v>
@@ -11682,7 +11680,7 @@
         <v>111</v>
       </c>
       <c r="AT37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU37" t="s">
         <v>118</v>
@@ -11963,7 +11961,7 @@
         <v>107</v>
       </c>
       <c r="AT38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU38" t="s">
         <v>118</v>
@@ -12821,7 +12819,7 @@
         <v>107</v>
       </c>
       <c r="AT41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU41" t="s">
         <v>118</v>
@@ -13114,7 +13112,7 @@
         <v>111</v>
       </c>
       <c r="AT42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU42" t="s">
         <v>118</v>
@@ -13398,13 +13396,13 @@
         <v>118</v>
       </c>
       <c r="AR43" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="AS43" t="s">
         <v>107</v>
       </c>
       <c r="AT43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU43" t="s">
         <v>118</v>
@@ -13978,7 +13976,7 @@
         <v>111</v>
       </c>
       <c r="AT45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU45" t="s">
         <v>118</v>
@@ -14549,7 +14547,7 @@
         <v>111</v>
       </c>
       <c r="AT47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU47" t="s">
         <v>118</v>
@@ -15132,7 +15130,7 @@
         <v>107</v>
       </c>
       <c r="AT49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU49" t="s">
         <v>118</v>
@@ -15416,7 +15414,7 @@
         <v>111</v>
       </c>
       <c r="AT50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU50" t="s">
         <v>118</v>
@@ -16585,7 +16583,7 @@
         <v>107</v>
       </c>
       <c r="AT54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU54" t="s">
         <v>118</v>
@@ -17455,7 +17453,7 @@
         <v>111</v>
       </c>
       <c r="AT57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU57" t="s">
         <v>118</v>
@@ -17736,7 +17734,7 @@
         <v>111</v>
       </c>
       <c r="AT58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU58" t="s">
         <v>118</v>
@@ -18908,7 +18906,7 @@
         <v>107</v>
       </c>
       <c r="AT62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU62" t="s">
         <v>118</v>
@@ -19204,7 +19202,7 @@
         <v>107</v>
       </c>
       <c r="AT63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU63" t="s">
         <v>118</v>
@@ -20068,7 +20066,7 @@
         <v>111</v>
       </c>
       <c r="AT66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU66" t="s">
         <v>118</v>
@@ -20352,7 +20350,7 @@
         <v>107</v>
       </c>
       <c r="AT67" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU67" t="s">
         <v>118</v>
@@ -21216,7 +21214,7 @@
         <v>111</v>
       </c>
       <c r="AT70" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU70" t="s">
         <v>118</v>
@@ -21805,7 +21803,7 @@
         <v>111</v>
       </c>
       <c r="AT72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU72" t="s">
         <v>118</v>
@@ -22095,7 +22093,7 @@
         <v>107</v>
       </c>
       <c r="AT73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU73" t="s">
         <v>118</v>
@@ -22382,7 +22380,7 @@
         <v>107</v>
       </c>
       <c r="AT74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU74" t="s">
         <v>118</v>
@@ -22965,7 +22963,7 @@
         <v>111</v>
       </c>
       <c r="AT76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU76" t="s">
         <v>118</v>
@@ -23255,7 +23253,7 @@
         <v>107</v>
       </c>
       <c r="AT77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU77" t="s">
         <v>118</v>
@@ -24125,7 +24123,7 @@
         <v>107</v>
       </c>
       <c r="AT80" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU80" t="s">
         <v>118</v>
@@ -24409,7 +24407,7 @@
         <v>107</v>
       </c>
       <c r="AT81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU81" t="s">
         <v>118</v>
@@ -25859,7 +25857,7 @@
         <v>107</v>
       </c>
       <c r="AT86" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU86" t="s">
         <v>118</v>
@@ -29940,7 +29938,7 @@
         <v>111</v>
       </c>
       <c r="AT100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU100" t="s">
         <v>118</v>
@@ -30212,7 +30210,7 @@
         <v>1</v>
       </c>
       <c r="AR101" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AS101" t="s">
         <v>111</v>
@@ -31372,7 +31370,7 @@
         <v>111</v>
       </c>
       <c r="AT105" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU105" t="s">
         <v>118</v>
@@ -34825,7 +34823,7 @@
         <v>111</v>
       </c>
       <c r="AT117" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU117" t="s">
         <v>118</v>
@@ -35396,7 +35394,7 @@
         <v>111</v>
       </c>
       <c r="AT119" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU119" t="s">
         <v>118</v>
@@ -35686,7 +35684,7 @@
         <v>111</v>
       </c>
       <c r="AT120" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU120" t="s">
         <v>118</v>
@@ -36547,7 +36545,7 @@
         <v>111</v>
       </c>
       <c r="AT123" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU123" t="s">
         <v>118</v>
@@ -36834,7 +36832,7 @@
         <v>111</v>
       </c>
       <c r="AT124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU124" t="s">
         <v>118</v>
@@ -38571,7 +38569,7 @@
         <v>107</v>
       </c>
       <c r="AT130" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU130" t="s">
         <v>118</v>
@@ -38858,7 +38856,7 @@
         <v>111</v>
       </c>
       <c r="AT131" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AU131" t="s">
         <v>118</v>
@@ -40296,7 +40294,7 @@
         <v>107</v>
       </c>
       <c r="AT136" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AU136" t="s">
         <v>118</v>

--- a/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
+++ b/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-7 ---\V3\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABA3EAE-3466-4B47-AD2C-0366604A3AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F58183-4AC6-4D59-ACCA-400274DCEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9765" yWindow="60" windowWidth="17250" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$DA$136</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11309" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11249" uniqueCount="259">
   <si>
     <t>mobile</t>
   </si>
@@ -736,9 +739,6 @@
     <t>2,7</t>
   </si>
   <si>
-    <t>1,a</t>
-  </si>
-  <si>
     <t>2,3,4,5</t>
   </si>
   <si>
@@ -748,25 +748,13 @@
     <t>1,2,3</t>
   </si>
   <si>
-    <t>1,b</t>
-  </si>
-  <si>
     <t>3,6,7</t>
-  </si>
-  <si>
-    <t>1ab</t>
-  </si>
-  <si>
-    <t>1b</t>
   </si>
   <si>
     <t>1,6,3,7</t>
   </si>
   <si>
     <t>6,10</t>
-  </si>
-  <si>
-    <t>1a</t>
   </si>
   <si>
     <t>1,4,7</t>
@@ -1155,6 +1143,7 @@
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="43" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1616,8 +1605,8 @@
       <c r="BB2" t="s">
         <v>123</v>
       </c>
-      <c r="BC2" t="s">
-        <v>105</v>
+      <c r="BC2">
+        <v>2</v>
       </c>
       <c r="BD2" t="s">
         <v>107</v>
@@ -1883,7 +1872,7 @@
         <v>111</v>
       </c>
       <c r="AT3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU3" t="s">
         <v>118</v>
@@ -2161,7 +2150,7 @@
         <v>146</v>
       </c>
       <c r="AR4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AS4" t="s">
         <v>107</v>
@@ -2193,8 +2182,8 @@
       <c r="BB4" t="s">
         <v>148</v>
       </c>
-      <c r="BC4" t="s">
-        <v>105</v>
+      <c r="BC4">
+        <v>2</v>
       </c>
       <c r="BD4" t="s">
         <v>149</v>
@@ -2460,7 +2449,7 @@
         <v>118</v>
       </c>
       <c r="AV5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AW5" t="s">
         <v>120</v>
@@ -2750,7 +2739,7 @@
         <v>107</v>
       </c>
       <c r="AT6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU6" t="s">
         <v>118</v>
@@ -3031,7 +3020,7 @@
         <v>107</v>
       </c>
       <c r="AT7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU7" t="s">
         <v>118</v>
@@ -3309,7 +3298,7 @@
         <v>105</v>
       </c>
       <c r="AT8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU8" t="s">
         <v>118</v>
@@ -3622,8 +3611,8 @@
       <c r="BB9" t="s">
         <v>148</v>
       </c>
-      <c r="BC9" t="s">
-        <v>118</v>
+      <c r="BC9">
+        <v>2</v>
       </c>
       <c r="BD9" t="s">
         <v>158</v>
@@ -3889,7 +3878,7 @@
         <v>107</v>
       </c>
       <c r="AT10" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU10" t="s">
         <v>118</v>
@@ -4170,7 +4159,7 @@
         <v>107</v>
       </c>
       <c r="AT11" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU11" t="s">
         <v>118</v>
@@ -4477,8 +4466,8 @@
       <c r="BB12" t="s">
         <v>148</v>
       </c>
-      <c r="BC12" t="s">
-        <v>105</v>
+      <c r="BC12">
+        <v>2</v>
       </c>
       <c r="BD12" t="s">
         <v>158</v>
@@ -4767,8 +4756,8 @@
       <c r="BB13" t="s">
         <v>148</v>
       </c>
-      <c r="BC13" t="s">
-        <v>105</v>
+      <c r="BC13">
+        <v>2</v>
       </c>
       <c r="BD13" t="s">
         <v>158</v>
@@ -5028,7 +5017,7 @@
         <v>107</v>
       </c>
       <c r="AT14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU14" t="s">
         <v>118</v>
@@ -5306,7 +5295,7 @@
         <v>107</v>
       </c>
       <c r="AT15" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU15" t="s">
         <v>118</v>
@@ -5593,7 +5582,7 @@
         <v>111</v>
       </c>
       <c r="AT16" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU16" t="s">
         <v>118</v>
@@ -5877,13 +5866,13 @@
         <v>186</v>
       </c>
       <c r="AR17" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AS17" t="s">
         <v>107</v>
       </c>
       <c r="AT17" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU17" t="s">
         <v>118</v>
@@ -6176,7 +6165,7 @@
         <v>107</v>
       </c>
       <c r="AT18" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU18" t="s">
         <v>118</v>
@@ -6463,7 +6452,7 @@
         <v>107</v>
       </c>
       <c r="AT19" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU19" t="s">
         <v>118</v>
@@ -6782,8 +6771,8 @@
       <c r="BB20" t="s">
         <v>123</v>
       </c>
-      <c r="BC20" t="s">
-        <v>118</v>
+      <c r="BC20">
+        <v>2</v>
       </c>
       <c r="BD20" t="s">
         <v>107</v>
@@ -7069,8 +7058,8 @@
       <c r="BB21" t="s">
         <v>148</v>
       </c>
-      <c r="BC21" t="s">
-        <v>118</v>
+      <c r="BC21">
+        <v>2</v>
       </c>
       <c r="BD21" t="s">
         <v>158</v>
@@ -7333,7 +7322,7 @@
         <v>107</v>
       </c>
       <c r="AT22" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU22" t="s">
         <v>118</v>
@@ -7620,7 +7609,7 @@
         <v>111</v>
       </c>
       <c r="AT23" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU23" t="s">
         <v>118</v>
@@ -7646,8 +7635,8 @@
       <c r="BB23" t="s">
         <v>148</v>
       </c>
-      <c r="BC23" t="s">
-        <v>105</v>
+      <c r="BC23">
+        <v>2</v>
       </c>
       <c r="BD23" t="s">
         <v>192</v>
@@ -7939,8 +7928,8 @@
       <c r="BB24" t="s">
         <v>148</v>
       </c>
-      <c r="BC24" t="s">
-        <v>105</v>
+      <c r="BC24">
+        <v>2</v>
       </c>
       <c r="BD24" t="s">
         <v>158</v>
@@ -8206,7 +8195,7 @@
         <v>111</v>
       </c>
       <c r="AT25" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU25" t="s">
         <v>118</v>
@@ -8493,7 +8482,7 @@
         <v>107</v>
       </c>
       <c r="AT26" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU26" t="s">
         <v>118</v>
@@ -8780,7 +8769,7 @@
         <v>111</v>
       </c>
       <c r="AT27" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU27" t="s">
         <v>118</v>
@@ -9070,7 +9059,7 @@
         <v>107</v>
       </c>
       <c r="AT28" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU28" t="s">
         <v>118</v>
@@ -9386,8 +9375,8 @@
       <c r="BB29" t="s">
         <v>123</v>
       </c>
-      <c r="BC29" t="s">
-        <v>105</v>
+      <c r="BC29">
+        <v>2</v>
       </c>
       <c r="BD29" t="s">
         <v>107</v>
@@ -9653,7 +9642,7 @@
         <v>111</v>
       </c>
       <c r="AT30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU30" t="s">
         <v>118</v>
@@ -9969,8 +9958,8 @@
       <c r="BB31" t="s">
         <v>123</v>
       </c>
-      <c r="BC31" t="s">
-        <v>105</v>
+      <c r="BC31">
+        <v>2</v>
       </c>
       <c r="BD31" t="s">
         <v>134</v>
@@ -10236,7 +10225,7 @@
         <v>111</v>
       </c>
       <c r="AT32" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU32" t="s">
         <v>118</v>
@@ -10520,7 +10509,7 @@
         <v>107</v>
       </c>
       <c r="AT33" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU33" t="s">
         <v>118</v>
@@ -10810,7 +10799,7 @@
         <v>111</v>
       </c>
       <c r="AT34" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU34" t="s">
         <v>118</v>
@@ -11129,8 +11118,8 @@
       <c r="BB35" t="s">
         <v>123</v>
       </c>
-      <c r="BC35" t="s">
-        <v>134</v>
+      <c r="BC35">
+        <v>1</v>
       </c>
       <c r="BD35" t="s">
         <v>107</v>
@@ -11396,7 +11385,7 @@
         <v>111</v>
       </c>
       <c r="AT36" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU36" t="s">
         <v>118</v>
@@ -11680,7 +11669,7 @@
         <v>111</v>
       </c>
       <c r="AT37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU37" t="s">
         <v>118</v>
@@ -11961,7 +11950,7 @@
         <v>107</v>
       </c>
       <c r="AT38" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU38" t="s">
         <v>118</v>
@@ -12271,8 +12260,8 @@
       <c r="BB39" t="s">
         <v>148</v>
       </c>
-      <c r="BC39" t="s">
-        <v>134</v>
+      <c r="BC39">
+        <v>1</v>
       </c>
       <c r="BD39" t="s">
         <v>210</v>
@@ -12819,7 +12808,7 @@
         <v>107</v>
       </c>
       <c r="AT41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU41" t="s">
         <v>118</v>
@@ -13112,7 +13101,7 @@
         <v>111</v>
       </c>
       <c r="AT42" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU42" t="s">
         <v>118</v>
@@ -13402,7 +13391,7 @@
         <v>107</v>
       </c>
       <c r="AT43" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU43" t="s">
         <v>118</v>
@@ -13976,7 +13965,7 @@
         <v>111</v>
       </c>
       <c r="AT45" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU45" t="s">
         <v>118</v>
@@ -14286,8 +14275,8 @@
       <c r="BB46" t="s">
         <v>123</v>
       </c>
-      <c r="BC46" t="s">
-        <v>105</v>
+      <c r="BC46">
+        <v>2</v>
       </c>
       <c r="BD46" t="s">
         <v>216</v>
@@ -14547,7 +14536,7 @@
         <v>111</v>
       </c>
       <c r="AT47" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU47" t="s">
         <v>118</v>
@@ -14860,8 +14849,8 @@
       <c r="BB48" t="s">
         <v>148</v>
       </c>
-      <c r="BC48" t="s">
-        <v>105</v>
+      <c r="BC48">
+        <v>2</v>
       </c>
       <c r="BD48" t="s">
         <v>107</v>
@@ -15130,7 +15119,7 @@
         <v>107</v>
       </c>
       <c r="AT49" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU49" t="s">
         <v>118</v>
@@ -15414,7 +15403,7 @@
         <v>111</v>
       </c>
       <c r="AT50" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU50" t="s">
         <v>118</v>
@@ -15440,8 +15429,8 @@
       <c r="BB50" t="s">
         <v>123</v>
       </c>
-      <c r="BC50" t="s">
-        <v>116</v>
+      <c r="BC50">
+        <v>1</v>
       </c>
       <c r="BD50" t="s">
         <v>107</v>
@@ -15739,8 +15728,8 @@
       <c r="BB51" t="s">
         <v>123</v>
       </c>
-      <c r="BC51" t="s">
-        <v>105</v>
+      <c r="BC51">
+        <v>2</v>
       </c>
       <c r="BD51" t="s">
         <v>158</v>
@@ -16029,8 +16018,8 @@
       <c r="BB52" t="s">
         <v>148</v>
       </c>
-      <c r="BC52" t="s">
-        <v>105</v>
+      <c r="BC52">
+        <v>2</v>
       </c>
       <c r="BD52" t="s">
         <v>107</v>
@@ -16583,7 +16572,7 @@
         <v>107</v>
       </c>
       <c r="AT54" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU54" t="s">
         <v>118</v>
@@ -16896,8 +16885,8 @@
       <c r="BB55" t="s">
         <v>148</v>
       </c>
-      <c r="BC55" t="s">
-        <v>118</v>
+      <c r="BC55">
+        <v>2</v>
       </c>
       <c r="BD55" t="s">
         <v>225</v>
@@ -17186,8 +17175,8 @@
       <c r="BB56" t="s">
         <v>148</v>
       </c>
-      <c r="BC56" t="s">
-        <v>134</v>
+      <c r="BC56">
+        <v>1</v>
       </c>
       <c r="BD56" t="s">
         <v>107</v>
@@ -17453,7 +17442,7 @@
         <v>111</v>
       </c>
       <c r="AT57" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU57" t="s">
         <v>118</v>
@@ -17734,7 +17723,7 @@
         <v>111</v>
       </c>
       <c r="AT58" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU58" t="s">
         <v>118</v>
@@ -17760,8 +17749,8 @@
       <c r="BB58" t="s">
         <v>123</v>
       </c>
-      <c r="BC58" t="s">
-        <v>107</v>
+      <c r="BC58">
+        <v>1</v>
       </c>
       <c r="BD58" t="s">
         <v>107</v>
@@ -18056,8 +18045,8 @@
       <c r="BB59" t="s">
         <v>123</v>
       </c>
-      <c r="BC59" t="s">
-        <v>134</v>
+      <c r="BC59">
+        <v>1</v>
       </c>
       <c r="BD59" t="s">
         <v>191</v>
@@ -18346,8 +18335,8 @@
       <c r="BB60" t="s">
         <v>123</v>
       </c>
-      <c r="BC60" t="s">
-        <v>134</v>
+      <c r="BC60">
+        <v>1</v>
       </c>
       <c r="BD60" t="s">
         <v>107</v>
@@ -18645,8 +18634,8 @@
       <c r="BB61" t="s">
         <v>148</v>
       </c>
-      <c r="BC61" t="s">
-        <v>134</v>
+      <c r="BC61">
+        <v>1</v>
       </c>
       <c r="BD61" t="s">
         <v>107</v>
@@ -18906,7 +18895,7 @@
         <v>107</v>
       </c>
       <c r="AT62" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU62" t="s">
         <v>118</v>
@@ -18932,8 +18921,8 @@
       <c r="BB62" t="s">
         <v>148</v>
       </c>
-      <c r="BC62" t="s">
-        <v>134</v>
+      <c r="BC62">
+        <v>1</v>
       </c>
       <c r="BD62" t="s">
         <v>216</v>
@@ -19202,7 +19191,7 @@
         <v>107</v>
       </c>
       <c r="AT63" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU63" t="s">
         <v>118</v>
@@ -19228,8 +19217,8 @@
       <c r="BB63" t="s">
         <v>123</v>
       </c>
-      <c r="BC63" t="s">
-        <v>105</v>
+      <c r="BC63">
+        <v>2</v>
       </c>
       <c r="BD63" t="s">
         <v>158</v>
@@ -19515,8 +19504,8 @@
       <c r="BB64" t="s">
         <v>148</v>
       </c>
-      <c r="BC64" t="s">
-        <v>105</v>
+      <c r="BC64">
+        <v>2</v>
       </c>
       <c r="BD64" t="s">
         <v>107</v>
@@ -19802,8 +19791,8 @@
       <c r="BB65" t="s">
         <v>123</v>
       </c>
-      <c r="BC65" t="s">
-        <v>105</v>
+      <c r="BC65">
+        <v>2</v>
       </c>
       <c r="BD65" t="s">
         <v>107</v>
@@ -20066,7 +20055,7 @@
         <v>111</v>
       </c>
       <c r="AT66" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU66" t="s">
         <v>118</v>
@@ -20350,7 +20339,7 @@
         <v>107</v>
       </c>
       <c r="AT67" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU67" t="s">
         <v>118</v>
@@ -20660,8 +20649,8 @@
       <c r="BB68" t="s">
         <v>148</v>
       </c>
-      <c r="BC68" t="s">
-        <v>105</v>
+      <c r="BC68">
+        <v>2</v>
       </c>
       <c r="BD68" t="s">
         <v>158</v>
@@ -20950,8 +20939,8 @@
       <c r="BB69" t="s">
         <v>148</v>
       </c>
-      <c r="BC69" t="s">
-        <v>105</v>
+      <c r="BC69">
+        <v>2</v>
       </c>
       <c r="BD69" t="s">
         <v>107</v>
@@ -21214,7 +21203,7 @@
         <v>111</v>
       </c>
       <c r="AT70" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU70" t="s">
         <v>118</v>
@@ -21240,8 +21229,8 @@
       <c r="BB70" t="s">
         <v>123</v>
       </c>
-      <c r="BC70" t="s">
-        <v>134</v>
+      <c r="BC70">
+        <v>1</v>
       </c>
       <c r="BD70" t="s">
         <v>107</v>
@@ -21539,8 +21528,8 @@
       <c r="BB71" t="s">
         <v>123</v>
       </c>
-      <c r="BC71" t="s">
-        <v>134</v>
+      <c r="BC71">
+        <v>1</v>
       </c>
       <c r="BD71" t="s">
         <v>158</v>
@@ -21803,7 +21792,7 @@
         <v>111</v>
       </c>
       <c r="AT72" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU72" t="s">
         <v>118</v>
@@ -21829,8 +21818,8 @@
       <c r="BB72" t="s">
         <v>148</v>
       </c>
-      <c r="BC72" t="s">
-        <v>118</v>
+      <c r="BC72">
+        <v>1</v>
       </c>
       <c r="BD72" t="s">
         <v>107</v>
@@ -22093,7 +22082,7 @@
         <v>107</v>
       </c>
       <c r="AT73" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU73" t="s">
         <v>118</v>
@@ -22380,7 +22369,7 @@
         <v>107</v>
       </c>
       <c r="AT74" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU74" t="s">
         <v>118</v>
@@ -22406,8 +22395,8 @@
       <c r="BB74" t="s">
         <v>148</v>
       </c>
-      <c r="BC74" t="s">
-        <v>105</v>
+      <c r="BC74">
+        <v>2</v>
       </c>
       <c r="BD74" t="s">
         <v>158</v>
@@ -22705,8 +22694,8 @@
       <c r="BB75" t="s">
         <v>148</v>
       </c>
-      <c r="BC75" t="s">
-        <v>118</v>
+      <c r="BC75">
+        <v>1</v>
       </c>
       <c r="BD75" t="s">
         <v>182</v>
@@ -22957,13 +22946,13 @@
         <v>216</v>
       </c>
       <c r="AR76" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AS76" t="s">
         <v>111</v>
       </c>
       <c r="AT76" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU76" t="s">
         <v>118</v>
@@ -23253,7 +23242,7 @@
         <v>107</v>
       </c>
       <c r="AT77" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU77" t="s">
         <v>118</v>
@@ -23563,8 +23552,8 @@
       <c r="BB78" t="s">
         <v>123</v>
       </c>
-      <c r="BC78" t="s">
-        <v>105</v>
+      <c r="BC78">
+        <v>2</v>
       </c>
       <c r="BD78" t="s">
         <v>107</v>
@@ -23859,8 +23848,8 @@
       <c r="BB79" t="s">
         <v>123</v>
       </c>
-      <c r="BC79" t="s">
-        <v>134</v>
+      <c r="BC79">
+        <v>1</v>
       </c>
       <c r="BD79" t="s">
         <v>158</v>
@@ -24123,7 +24112,7 @@
         <v>107</v>
       </c>
       <c r="AT80" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU80" t="s">
         <v>118</v>
@@ -24407,7 +24396,7 @@
         <v>107</v>
       </c>
       <c r="AT81" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU81" t="s">
         <v>118</v>
@@ -24720,8 +24709,8 @@
       <c r="BB82" t="s">
         <v>148</v>
       </c>
-      <c r="BC82" t="s">
-        <v>105</v>
+      <c r="BC82">
+        <v>2</v>
       </c>
       <c r="BD82" t="s">
         <v>107</v>
@@ -25303,8 +25292,8 @@
       <c r="BB84" t="s">
         <v>148</v>
       </c>
-      <c r="BC84" t="s">
-        <v>238</v>
+      <c r="BC84">
+        <v>1</v>
       </c>
       <c r="BD84" t="s">
         <v>107</v>
@@ -25558,10 +25547,10 @@
         <v>0</v>
       </c>
       <c r="AQ85" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR85" t="s">
         <v>239</v>
-      </c>
-      <c r="AR85" t="s">
-        <v>240</v>
       </c>
       <c r="AS85" t="s">
         <v>107</v>
@@ -25593,14 +25582,14 @@
       <c r="BB85" t="s">
         <v>123</v>
       </c>
-      <c r="BC85" t="s">
-        <v>238</v>
+      <c r="BC85">
+        <v>1</v>
       </c>
       <c r="BD85" t="s">
         <v>105</v>
       </c>
       <c r="BE85" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BF85">
         <v>30</v>
@@ -25857,7 +25846,7 @@
         <v>107</v>
       </c>
       <c r="AT86" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU86" t="s">
         <v>118</v>
@@ -26170,8 +26159,11 @@
       <c r="BA87" t="s">
         <v>122</v>
       </c>
-      <c r="BC87" t="s">
-        <v>238</v>
+      <c r="BB87" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC87">
+        <v>1</v>
       </c>
       <c r="BD87" t="s">
         <v>107</v>
@@ -26460,11 +26452,11 @@
       <c r="BB88" t="s">
         <v>123</v>
       </c>
-      <c r="BC88" t="s">
-        <v>242</v>
+      <c r="BC88">
+        <v>1</v>
       </c>
       <c r="BD88" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="BE88" t="s">
         <v>150</v>
@@ -26750,8 +26742,8 @@
       <c r="BB89" t="s">
         <v>123</v>
       </c>
-      <c r="BC89" t="s">
-        <v>116</v>
+      <c r="BC89">
+        <v>1</v>
       </c>
       <c r="BD89" t="s">
         <v>107</v>
@@ -27040,8 +27032,8 @@
       <c r="BB90" t="s">
         <v>148</v>
       </c>
-      <c r="BC90" t="s">
-        <v>244</v>
+      <c r="BC90">
+        <v>1</v>
       </c>
       <c r="BD90" t="s">
         <v>158</v>
@@ -27333,8 +27325,8 @@
       <c r="BB91" t="s">
         <v>148</v>
       </c>
-      <c r="BC91" t="s">
-        <v>244</v>
+      <c r="BC91">
+        <v>1</v>
       </c>
       <c r="BD91" t="s">
         <v>107</v>
@@ -27623,8 +27615,8 @@
       <c r="BB92" t="s">
         <v>123</v>
       </c>
-      <c r="BC92" t="s">
-        <v>244</v>
+      <c r="BC92">
+        <v>1</v>
       </c>
       <c r="BD92" t="s">
         <v>107</v>
@@ -27910,8 +27902,8 @@
       <c r="BB93" t="s">
         <v>123</v>
       </c>
-      <c r="BC93" t="s">
-        <v>116</v>
+      <c r="BC93">
+        <v>2</v>
       </c>
       <c r="BD93" t="s">
         <v>107</v>
@@ -28203,8 +28195,8 @@
       <c r="BB94" t="s">
         <v>123</v>
       </c>
-      <c r="BC94" t="s">
-        <v>245</v>
+      <c r="BC94">
+        <v>1</v>
       </c>
       <c r="BD94" t="s">
         <v>107</v>
@@ -28502,8 +28494,8 @@
       <c r="BB95" t="s">
         <v>123</v>
       </c>
-      <c r="BC95" t="s">
-        <v>245</v>
+      <c r="BC95">
+        <v>1</v>
       </c>
       <c r="BD95" t="s">
         <v>107</v>
@@ -28793,7 +28785,7 @@
         <v>105</v>
       </c>
       <c r="BD96" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="BE96" t="s">
         <v>107</v>
@@ -29029,7 +29021,7 @@
         <v>105</v>
       </c>
       <c r="AK97" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AL97">
         <v>1</v>
@@ -29082,8 +29074,8 @@
       <c r="BB97" t="s">
         <v>123</v>
       </c>
-      <c r="BC97" t="s">
-        <v>107</v>
+      <c r="BC97">
+        <v>1</v>
       </c>
       <c r="BD97" t="s">
         <v>107</v>
@@ -29665,8 +29657,8 @@
       <c r="BB99" t="s">
         <v>148</v>
       </c>
-      <c r="BC99" t="s">
-        <v>245</v>
+      <c r="BC99">
+        <v>1</v>
       </c>
       <c r="BD99" t="s">
         <v>107</v>
@@ -29938,7 +29930,7 @@
         <v>111</v>
       </c>
       <c r="AT100" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU100" t="s">
         <v>118</v>
@@ -29961,8 +29953,11 @@
       <c r="BA100" t="s">
         <v>122</v>
       </c>
-      <c r="BC100" t="s">
-        <v>105</v>
+      <c r="BB100" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC100">
+        <v>2</v>
       </c>
       <c r="BD100" t="s">
         <v>107</v>
@@ -30210,7 +30205,7 @@
         <v>1</v>
       </c>
       <c r="AR101" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AS101" t="s">
         <v>111</v>
@@ -30242,8 +30237,8 @@
       <c r="BB101" t="s">
         <v>123</v>
       </c>
-      <c r="BC101" t="s">
-        <v>245</v>
+      <c r="BC101">
+        <v>1</v>
       </c>
       <c r="BD101" t="s">
         <v>107</v>
@@ -30529,8 +30524,8 @@
       <c r="BB102" t="s">
         <v>148</v>
       </c>
-      <c r="BC102" t="s">
-        <v>245</v>
+      <c r="BC102">
+        <v>1</v>
       </c>
       <c r="BD102" t="s">
         <v>107</v>
@@ -30816,8 +30811,11 @@
       <c r="BA103" t="s">
         <v>122</v>
       </c>
-      <c r="BC103" t="s">
-        <v>248</v>
+      <c r="BB103" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC103">
+        <v>1</v>
       </c>
       <c r="BD103" t="s">
         <v>107</v>
@@ -31103,6 +31101,9 @@
       <c r="BA104" t="s">
         <v>121</v>
       </c>
+      <c r="BB104" t="s">
+        <v>148</v>
+      </c>
       <c r="BC104" t="s">
         <v>107</v>
       </c>
@@ -31370,7 +31371,7 @@
         <v>111</v>
       </c>
       <c r="AT105" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU105" t="s">
         <v>118</v>
@@ -31393,8 +31394,11 @@
       <c r="BA105" t="s">
         <v>122</v>
       </c>
-      <c r="BC105" t="s">
+      <c r="BB105" t="s">
         <v>245</v>
+      </c>
+      <c r="BC105">
+        <v>1</v>
       </c>
       <c r="BD105" t="s">
         <v>107</v>
@@ -31680,8 +31684,8 @@
       <c r="BB106" t="s">
         <v>148</v>
       </c>
-      <c r="BC106" t="s">
-        <v>244</v>
+      <c r="BC106">
+        <v>1</v>
       </c>
       <c r="BD106" t="s">
         <v>107</v>
@@ -31967,14 +31971,17 @@
       <c r="BA107" t="s">
         <v>122</v>
       </c>
-      <c r="BC107" t="s">
+      <c r="BB107" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC107">
+        <v>1</v>
+      </c>
+      <c r="BD107" t="s">
+        <v>107</v>
+      </c>
+      <c r="BE107" t="s">
         <v>244</v>
-      </c>
-      <c r="BD107" t="s">
-        <v>107</v>
-      </c>
-      <c r="BE107" t="s">
-        <v>249</v>
       </c>
       <c r="BF107">
         <v>8</v>
@@ -32254,8 +32261,11 @@
       <c r="BA108" t="s">
         <v>122</v>
       </c>
-      <c r="BC108" t="s">
-        <v>116</v>
+      <c r="BB108" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC108">
+        <v>1</v>
       </c>
       <c r="BD108" t="s">
         <v>107</v>
@@ -32544,8 +32554,8 @@
       <c r="BB109" t="s">
         <v>123</v>
       </c>
-      <c r="BC109" t="s">
-        <v>116</v>
+      <c r="BC109">
+        <v>1</v>
       </c>
       <c r="BD109" t="s">
         <v>107</v>
@@ -32829,10 +32839,10 @@
         <v>122</v>
       </c>
       <c r="BB110" t="s">
-        <v>250</v>
-      </c>
-      <c r="BC110" t="s">
-        <v>107</v>
+        <v>245</v>
+      </c>
+      <c r="BC110">
+        <v>1</v>
       </c>
       <c r="BD110" t="s">
         <v>139</v>
@@ -33118,8 +33128,8 @@
       <c r="BB111" t="s">
         <v>123</v>
       </c>
-      <c r="BC111" t="s">
-        <v>116</v>
+      <c r="BC111">
+        <v>1</v>
       </c>
       <c r="BD111" t="s">
         <v>222</v>
@@ -33695,8 +33705,8 @@
       <c r="BB113" t="s">
         <v>123</v>
       </c>
-      <c r="BC113" t="s">
-        <v>245</v>
+      <c r="BC113">
+        <v>1</v>
       </c>
       <c r="BD113" t="s">
         <v>109</v>
@@ -33988,8 +33998,8 @@
       <c r="BB114" t="s">
         <v>123</v>
       </c>
-      <c r="BC114" t="s">
-        <v>116</v>
+      <c r="BC114">
+        <v>2</v>
       </c>
       <c r="BD114" t="s">
         <v>107</v>
@@ -34275,8 +34285,8 @@
       <c r="BB115" t="s">
         <v>123</v>
       </c>
-      <c r="BC115" t="s">
-        <v>116</v>
+      <c r="BC115">
+        <v>2</v>
       </c>
       <c r="BD115" t="s">
         <v>134</v>
@@ -34565,8 +34575,11 @@
       <c r="BA116" t="s">
         <v>122</v>
       </c>
-      <c r="BC116" t="s">
-        <v>244</v>
+      <c r="BB116" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC116">
+        <v>1</v>
       </c>
       <c r="BD116" t="s">
         <v>107</v>
@@ -34823,7 +34836,7 @@
         <v>111</v>
       </c>
       <c r="AT117" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU117" t="s">
         <v>118</v>
@@ -35394,7 +35407,7 @@
         <v>111</v>
       </c>
       <c r="AT119" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU119" t="s">
         <v>118</v>
@@ -35684,7 +35697,7 @@
         <v>111</v>
       </c>
       <c r="AT120" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU120" t="s">
         <v>118</v>
@@ -35991,8 +36004,11 @@
       <c r="BA121" t="s">
         <v>122</v>
       </c>
-      <c r="BC121" t="s">
-        <v>245</v>
+      <c r="BB121" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC121">
+        <v>1</v>
       </c>
       <c r="BD121" t="s">
         <v>107</v>
@@ -36545,7 +36561,7 @@
         <v>111</v>
       </c>
       <c r="AT123" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU123" t="s">
         <v>118</v>
@@ -36832,7 +36848,7 @@
         <v>111</v>
       </c>
       <c r="AT124" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU124" t="s">
         <v>118</v>
@@ -36859,7 +36875,7 @@
         <v>107</v>
       </c>
       <c r="BD124" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="BE124" t="s">
         <v>105</v>
@@ -37373,7 +37389,7 @@
         <v>105</v>
       </c>
       <c r="AK126" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AL126">
         <v>12</v>
@@ -37391,10 +37407,10 @@
         <v>4</v>
       </c>
       <c r="AQ126" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AR126" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AS126" t="s">
         <v>111</v>
@@ -37687,7 +37703,7 @@
         <v>1</v>
       </c>
       <c r="AQ127" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AR127" t="s">
         <v>147</v>
@@ -37726,7 +37742,7 @@
         <v>107</v>
       </c>
       <c r="BE127" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="BF127">
         <v>24</v>
@@ -38006,8 +38022,11 @@
       <c r="BA128" t="s">
         <v>122</v>
       </c>
-      <c r="BC128" t="s">
-        <v>116</v>
+      <c r="BB128" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC128">
+        <v>1</v>
       </c>
       <c r="BD128" t="s">
         <v>182</v>
@@ -38297,10 +38316,10 @@
         <v>122</v>
       </c>
       <c r="BB129" t="s">
-        <v>250</v>
-      </c>
-      <c r="BC129" t="s">
         <v>245</v>
+      </c>
+      <c r="BC129">
+        <v>1</v>
       </c>
       <c r="BD129" t="s">
         <v>107</v>
@@ -38569,7 +38588,7 @@
         <v>107</v>
       </c>
       <c r="AT130" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU130" t="s">
         <v>118</v>
@@ -38599,7 +38618,7 @@
         <v>158</v>
       </c>
       <c r="BE130" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BF130">
         <v>2</v>
@@ -38856,7 +38875,7 @@
         <v>111</v>
       </c>
       <c r="AT131" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AU131" t="s">
         <v>118</v>
@@ -38886,7 +38905,7 @@
         <v>134</v>
       </c>
       <c r="BE131" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="BF131">
         <v>9</v>
@@ -39170,7 +39189,7 @@
         <v>195</v>
       </c>
       <c r="BE132" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BF132">
         <v>6</v>
@@ -39424,7 +39443,7 @@
         <v>186</v>
       </c>
       <c r="AR133" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AS133" t="s">
         <v>107</v>
@@ -39456,8 +39475,8 @@
       <c r="BB133" t="s">
         <v>123</v>
       </c>
-      <c r="BC133" t="s">
-        <v>105</v>
+      <c r="BC133">
+        <v>2</v>
       </c>
       <c r="BD133" t="s">
         <v>216</v>
@@ -39740,8 +39759,11 @@
       <c r="BA134" t="s">
         <v>122</v>
       </c>
-      <c r="BC134" t="s">
+      <c r="BB134" t="s">
         <v>245</v>
+      </c>
+      <c r="BC134">
+        <v>1</v>
       </c>
       <c r="BD134" t="s">
         <v>107</v>
@@ -39980,7 +40002,7 @@
         <v>105</v>
       </c>
       <c r="AK135" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AL135">
         <v>12</v>
@@ -40030,8 +40052,11 @@
       <c r="BA135" t="s">
         <v>122</v>
       </c>
-      <c r="BC135" t="s">
+      <c r="BB135" t="s">
         <v>245</v>
+      </c>
+      <c r="BC135">
+        <v>1</v>
       </c>
       <c r="BD135" t="s">
         <v>107</v>
@@ -40294,7 +40319,7 @@
         <v>107</v>
       </c>
       <c r="AT136" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AU136" t="s">
         <v>118</v>
